--- a/docs/ethnicityCategory.xlsx
+++ b/docs/ethnicityCategory.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="52">
   <si>
     <t>Property</t>
   </si>
@@ -31,18 +31,21 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
   </si>
   <si>
+    <t>EthnicityCategory</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
     <t>ethnicityCategory</t>
   </si>
   <si>
-    <t>Title</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
@@ -58,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -82,7 +85,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t xml:space="preserve">Terminology Maps ethnicityCategory </t>
+    <t>Terminology Maps ethnicityCategory</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -344,91 +347,91 @@
         <v>8</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -443,80 +446,80 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C1" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>30</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>27</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="E2" t="s" s="2">
         <v>33</v>
-      </c>
-      <c r="E2" t="s" s="2">
-        <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="C5" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="D5" t="s" s="2">
         <v>42</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="C5" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="D5" t="s" s="2">
-        <v>41</v>
       </c>
       <c r="E5" s="2"/>
     </row>
@@ -532,65 +535,65 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C1" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>30</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>27</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E4" s="2"/>
     </row>

--- a/docs/ethnicityCategory.xlsx
+++ b/docs/ethnicityCategory.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ethnicityCategory.xlsx
+++ b/docs/ethnicityCategory.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ethnicityCategory.xlsx
+++ b/docs/ethnicityCategory.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ethnicityCategory.xlsx
+++ b/docs/ethnicityCategory.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ethnicityCategory.xlsx
+++ b/docs/ethnicityCategory.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ethnicityCategory.xlsx
+++ b/docs/ethnicityCategory.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ethnicityCategory.xlsx
+++ b/docs/ethnicityCategory.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ethnicityCategory.xlsx
+++ b/docs/ethnicityCategory.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
